--- a/Hardware/Td5_OBD2_PickAndPlace.xlsx
+++ b/Hardware/Td5_OBD2_PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB2_2026_09_11" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB2_2026_09_22" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="121">
   <si>
     <t>Designator</t>
   </si>
@@ -67,13 +67,13 @@
     <t>C0603</t>
   </si>
   <si>
-    <t>110.109mm</t>
-  </si>
-  <si>
-    <t>-10.414mm</t>
-  </si>
-  <si>
-    <t>-9.714mm</t>
+    <t>112.395mm</t>
+  </si>
+  <si>
+    <t>5.588mm</t>
+  </si>
+  <si>
+    <t>4.888mm</t>
   </si>
   <si>
     <t>T</t>
@@ -88,25 +88,22 @@
     <t>C2</t>
   </si>
   <si>
-    <t>125.095mm</t>
-  </si>
-  <si>
-    <t>-0.635mm</t>
-  </si>
-  <si>
-    <t>-1.335mm</t>
+    <t>106.045mm</t>
+  </si>
+  <si>
+    <t>-6.223mm</t>
+  </si>
+  <si>
+    <t>106.745mm</t>
   </si>
   <si>
     <t>C3</t>
   </si>
   <si>
-    <t>121.031mm</t>
-  </si>
-  <si>
-    <t>-3.048mm</t>
-  </si>
-  <si>
-    <t>-3.748mm</t>
+    <t>9.271mm</t>
+  </si>
+  <si>
+    <t>9.971mm</t>
   </si>
   <si>
     <t>D1</t>
@@ -118,13 +115,13 @@
     <t>LL-34_L3.5-W1.5-RD</t>
   </si>
   <si>
-    <t>119.634mm</t>
-  </si>
-  <si>
-    <t>-10.287mm</t>
-  </si>
-  <si>
-    <t>-11.987mm</t>
+    <t>109.347mm</t>
+  </si>
+  <si>
+    <t>8.509mm</t>
+  </si>
+  <si>
+    <t>10.209mm</t>
   </si>
   <si>
     <t>D2</t>
@@ -136,13 +133,13 @@
     <t>SMA_L4.3-W2.6-LS5.2-RD</t>
   </si>
   <si>
-    <t>116.586mm</t>
-  </si>
-  <si>
-    <t>-11.049mm</t>
-  </si>
-  <si>
-    <t>-13.249mm</t>
+    <t>98.679mm</t>
+  </si>
+  <si>
+    <t>-3.937mm</t>
+  </si>
+  <si>
+    <t>-6.137mm</t>
   </si>
   <si>
     <t>SS34</t>
@@ -151,13 +148,7 @@
     <t>D3</t>
   </si>
   <si>
-    <t>117.475mm</t>
-  </si>
-  <si>
-    <t>-2.921mm</t>
-  </si>
-  <si>
-    <t>-5.121mm</t>
+    <t>102.743mm</t>
   </si>
   <si>
     <t>R2</t>
@@ -169,115 +160,220 @@
     <t>R0603</t>
   </si>
   <si>
-    <t>121.412mm</t>
-  </si>
-  <si>
-    <t>0.381mm</t>
-  </si>
-  <si>
-    <t>120.659mm</t>
+    <t>109.982mm</t>
+  </si>
+  <si>
+    <t>-6.35mm</t>
+  </si>
+  <si>
+    <t>110.735mm</t>
   </si>
   <si>
     <t>1kΩ</t>
   </si>
   <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>E-L9637D013TR</t>
+  </si>
+  <si>
+    <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
+  </si>
+  <si>
+    <t>107.315mm</t>
+  </si>
+  <si>
+    <t>-0.381mm</t>
+  </si>
+  <si>
+    <t>105.41mm</t>
+  </si>
+  <si>
+    <t>-3.153mm</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>XIAO ESP32S3</t>
+  </si>
+  <si>
+    <t>COMM-SMD_KQ-2801_V106</t>
+  </si>
+  <si>
+    <t>123.571mm</t>
+  </si>
+  <si>
+    <t>1.524mm</t>
+  </si>
+  <si>
+    <t>131.871mm</t>
+  </si>
+  <si>
+    <t>-6.096mm</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R7BB104</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>8.382mm</t>
+  </si>
+  <si>
+    <t>7.962mm</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>0402WGF4702TCE</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>105.537mm</t>
+  </si>
+  <si>
+    <t>10.668mm</t>
+  </si>
+  <si>
+    <t>10.235mm</t>
+  </si>
+  <si>
+    <t>47kΩ</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>FRC0402F1002TS</t>
+  </si>
+  <si>
+    <t>7.949mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>K7805-500R3_C2992390</t>
+  </si>
+  <si>
+    <t>PWRM-TH_3P-L11.5-W7.6-P2.54_R-785.0-0.5</t>
+  </si>
+  <si>
+    <t>98.806mm</t>
+  </si>
+  <si>
+    <t>5.842mm</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>K7805-500R3</t>
+  </si>
+  <si>
+    <t>J*1</t>
+  </si>
+  <si>
+    <t>OBD2</t>
+  </si>
+  <si>
+    <t>OBD2_Male_R/A_Case</t>
+  </si>
+  <si>
+    <t>115.032mm</t>
+  </si>
+  <si>
+    <t>15.899mm</t>
+  </si>
+  <si>
+    <t>129.032mm</t>
+  </si>
+  <si>
+    <t>17.399mm</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>1RC0402J0513</t>
+  </si>
+  <si>
+    <t>111.125mm</t>
+  </si>
+  <si>
+    <t>-3.302mm</t>
+  </si>
+  <si>
+    <t>-3.735mm</t>
+  </si>
+  <si>
+    <t>51kΩ</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>TNPW040220K0BEED</t>
+  </si>
+  <si>
+    <t>110.998mm</t>
+  </si>
+  <si>
+    <t>-1.016mm</t>
+  </si>
+  <si>
+    <t>-1.449mm</t>
+  </si>
+  <si>
+    <t>20kΩ</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>TLV3691IDCKR</t>
+  </si>
+  <si>
+    <t>SC-70-5_L2.1-W1.3-P0.65-LS2.1-BR</t>
+  </si>
+  <si>
+    <t>111.76mm</t>
+  </si>
+  <si>
+    <t>110.66mm</t>
+  </si>
+  <si>
+    <t>2.174mm</t>
+  </si>
+  <si>
     <t>R3</t>
   </si>
   <si>
     <t>510R</t>
   </si>
   <si>
-    <t>124.841mm</t>
-  </si>
-  <si>
-    <t>-4.699mm</t>
-  </si>
-  <si>
-    <t>124.088mm</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>E-L9637D013TR</t>
-  </si>
-  <si>
-    <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>123.698mm</t>
-  </si>
-  <si>
-    <t>121.793mm</t>
-  </si>
-  <si>
-    <t>-13.186mm</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>XIAO ESP32S3</t>
-  </si>
-  <si>
-    <t>COMM-SMD_KQ-2801_V106</t>
-  </si>
-  <si>
-    <t>115.57mm</t>
-  </si>
-  <si>
-    <t>-4.572mm</t>
-  </si>
-  <si>
-    <t>107.95mm</t>
-  </si>
-  <si>
-    <t>3.728mm</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>OBD2</t>
-  </si>
-  <si>
-    <t>114.427mm</t>
-  </si>
-  <si>
-    <t>-26.797mm</t>
-  </si>
-  <si>
-    <t>128.427mm</t>
-  </si>
-  <si>
-    <t>-31.047mm</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>L7805ABD2T-TR</t>
-  </si>
-  <si>
-    <t>TO-263-2_L10.0-W9.2-P5.08-LS15.3-TL-CW</t>
-  </si>
-  <si>
-    <t>110.404mm</t>
-  </si>
-  <si>
-    <t>-5.113mm</t>
-  </si>
-  <si>
-    <t>107.864mm</t>
-  </si>
-  <si>
-    <t>-10.51mm</t>
+    <t>106.68mm</t>
+  </si>
+  <si>
+    <t>4.826mm</t>
+  </si>
+  <si>
+    <t>105.927mm</t>
   </si>
 </sst>
 </file>
@@ -654,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -742,7 +838,7 @@
         <v>21</v>
       </c>
       <c r="L2">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M2" t="s">
         <v>22</v>
@@ -777,10 +873,10 @@
         <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -789,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="L3">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M3" t="s">
         <v>22</v>
@@ -812,22 +908,22 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
         <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -836,7 +932,7 @@
         <v>21</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M4" t="s">
         <v>22</v>
@@ -850,31 +946,31 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
         <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -883,45 +979,45 @@
         <v>21</v>
       </c>
       <c r="L5">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M5" t="s">
         <v>22</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>41</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
         <v>42</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" t="s">
-        <v>43</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -936,39 +1032,39 @@
         <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -983,39 +1079,39 @@
         <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -1024,48 +1120,48 @@
         <v>21</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M8" t="s">
         <v>22</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" t="s">
+      <c r="E9" t="s">
         <v>57</v>
       </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
         <v>58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
       </c>
       <c r="I9" t="s">
         <v>59</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K9" t="s">
         <v>21</v>
@@ -1077,33 +1173,33 @@
         <v>22</v>
       </c>
       <c r="N9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>62</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>63</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
       <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
         <v>64</v>
-      </c>
-      <c r="G10" t="s">
-        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>65</v>
@@ -1112,22 +1208,22 @@
         <v>66</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
         <v>21</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M10" t="s">
         <v>22</v>
       </c>
       <c r="N10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1141,119 +1237,119 @@
         <v>69</v>
       </c>
       <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
         <v>70</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
         <v>71</v>
       </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" t="s">
-        <v>73</v>
-      </c>
       <c r="J11">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M11" t="s">
         <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>76</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
         <v>76</v>
       </c>
-      <c r="D12" t="s">
+      <c r="G12" t="s">
         <v>77</v>
       </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" t="s">
         <v>78</v>
       </c>
-      <c r="F12" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" t="s">
         <v>79</v>
       </c>
-      <c r="I12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12">
-        <v>16</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>81</v>
-      </c>
-      <c r="N12" t="s">
-        <v>76</v>
-      </c>
       <c r="O12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s">
         <v>82</v>
       </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" t="s">
-        <v>88</v>
-      </c>
       <c r="J13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="s">
         <v>21</v>
@@ -1269,6 +1365,288 @@
       </c>
       <c r="O13" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14">
+        <v>270</v>
+      </c>
+      <c r="M14" t="s">
+        <v>89</v>
+      </c>
+      <c r="N14" t="s">
+        <v>90</v>
+      </c>
+      <c r="O14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15">
+        <v>16</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15">
+        <v>270</v>
+      </c>
+      <c r="M15" t="s">
+        <v>89</v>
+      </c>
+      <c r="N15" t="s">
+        <v>92</v>
+      </c>
+      <c r="O15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>102</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16">
+        <v>90</v>
+      </c>
+      <c r="M16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s">
+        <v>103</v>
+      </c>
+      <c r="O16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17">
+        <v>90</v>
+      </c>
+      <c r="M17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s">
+        <v>109</v>
+      </c>
+      <c r="O17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
+      <c r="K18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18">
+        <v>180</v>
+      </c>
+      <c r="M18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s">
+        <v>111</v>
+      </c>
+      <c r="O18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s">
+        <v>117</v>
+      </c>
+      <c r="O19" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
